--- a/sample_data/C_legacy_pos/i-3-STOCK.xlsx
+++ b/sample_data/C_legacy_pos/i-3-STOCK.xlsx
@@ -479,10 +479,10 @@
         <v>18</v>
       </c>
       <c r="D5" t="n">
-        <v>44.46</v>
+        <v>33.52</v>
       </c>
       <c r="E5" t="n">
-        <v>800.28</v>
+        <v>603.36</v>
       </c>
     </row>
     <row r="6">
@@ -497,13 +497,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="D6" t="n">
-        <v>39.44</v>
+        <v>42.26</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>1014.24</v>
       </c>
     </row>
     <row r="7">
@@ -518,13 +518,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>82</v>
+        <v>9</v>
       </c>
       <c r="D7" t="n">
-        <v>50.05</v>
+        <v>47.66</v>
       </c>
       <c r="E7" t="n">
-        <v>4104.1</v>
+        <v>428.94</v>
       </c>
     </row>
     <row r="8">
@@ -539,13 +539,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>79</v>
+        <v>21</v>
       </c>
       <c r="D8" t="n">
-        <v>61.96</v>
+        <v>61.74</v>
       </c>
       <c r="E8" t="n">
-        <v>4894.84</v>
+        <v>1296.54</v>
       </c>
     </row>
     <row r="9">
@@ -560,13 +560,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>452</v>
+        <v>395</v>
       </c>
       <c r="D9" t="n">
-        <v>33.92</v>
+        <v>33.5</v>
       </c>
       <c r="E9" t="n">
-        <v>15331.84</v>
+        <v>13232.5</v>
       </c>
     </row>
     <row r="10">
@@ -581,13 +581,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="D10" t="n">
-        <v>30.17</v>
+        <v>40.4</v>
       </c>
       <c r="E10" t="n">
-        <v>693.91</v>
+        <v>1333.2</v>
       </c>
     </row>
     <row r="11">
@@ -602,13 +602,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="D11" t="n">
-        <v>141.69</v>
+        <v>135.21</v>
       </c>
       <c r="E11" t="n">
-        <v>1133.52</v>
+        <v>3650.67</v>
       </c>
     </row>
     <row r="12">
@@ -623,13 +623,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>56</v>
+        <v>19</v>
       </c>
       <c r="D12" t="n">
-        <v>102.98</v>
+        <v>101.8</v>
       </c>
       <c r="E12" t="n">
-        <v>5766.88</v>
+        <v>1934.2</v>
       </c>
     </row>
     <row r="13">
@@ -644,13 +644,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>119</v>
+        <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>127.67</v>
+        <v>122.05</v>
       </c>
       <c r="E13" t="n">
-        <v>15192.73</v>
+        <v>244.1</v>
       </c>
     </row>
     <row r="14">
@@ -665,13 +665,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>72</v>
+        <v>133</v>
       </c>
       <c r="D14" t="n">
-        <v>28.55</v>
+        <v>31.07</v>
       </c>
       <c r="E14" t="n">
-        <v>2055.6</v>
+        <v>4132.31</v>
       </c>
     </row>
     <row r="15">
@@ -686,13 +686,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D15" t="n">
-        <v>87.27</v>
+        <v>87.34</v>
       </c>
       <c r="E15" t="n">
-        <v>1309.05</v>
+        <v>960.74</v>
       </c>
     </row>
     <row r="16">
@@ -707,13 +707,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="D16" t="n">
-        <v>183.69</v>
+        <v>195.12</v>
       </c>
       <c r="E16" t="n">
-        <v>6245.46</v>
+        <v>1365.84</v>
       </c>
     </row>
     <row r="17">
@@ -728,13 +728,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>91</v>
+        <v>11</v>
       </c>
       <c r="D17" t="n">
-        <v>101.51</v>
+        <v>106.53</v>
       </c>
       <c r="E17" t="n">
-        <v>9237.41</v>
+        <v>1171.83</v>
       </c>
     </row>
     <row r="18">
@@ -752,10 +752,10 @@
         <v>19</v>
       </c>
       <c r="D18" t="n">
-        <v>78.38</v>
+        <v>77.53</v>
       </c>
       <c r="E18" t="n">
-        <v>1489.22</v>
+        <v>1473.07</v>
       </c>
     </row>
     <row r="19">
@@ -770,13 +770,13 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="D19" t="n">
-        <v>90.56</v>
+        <v>90.78</v>
       </c>
       <c r="E19" t="n">
-        <v>4437.44</v>
+        <v>907.8</v>
       </c>
     </row>
     <row r="20">
@@ -791,13 +791,13 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="D20" t="n">
-        <v>111.1</v>
+        <v>112.47</v>
       </c>
       <c r="E20" t="n">
-        <v>2555.3</v>
+        <v>2024.46</v>
       </c>
     </row>
     <row r="21">
@@ -812,13 +812,13 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>31</v>
+        <v>102</v>
       </c>
       <c r="D21" t="n">
-        <v>199.02</v>
+        <v>211.64</v>
       </c>
       <c r="E21" t="n">
-        <v>6169.62</v>
+        <v>21587.28</v>
       </c>
     </row>
     <row r="22">
@@ -833,13 +833,13 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="D22" t="n">
-        <v>226.56</v>
+        <v>243.25</v>
       </c>
       <c r="E22" t="n">
-        <v>16312.32</v>
+        <v>14351.75</v>
       </c>
     </row>
     <row r="23">
@@ -854,13 +854,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>119</v>
+        <v>58</v>
       </c>
       <c r="D23" t="n">
-        <v>11.82</v>
+        <v>11.21</v>
       </c>
       <c r="E23" t="n">
-        <v>1406.58</v>
+        <v>650.1799999999999</v>
       </c>
     </row>
     <row r="24">
@@ -875,13 +875,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="D24" t="n">
-        <v>261.7</v>
+        <v>268.13</v>
       </c>
       <c r="E24" t="n">
-        <v>2617</v>
+        <v>5898.86</v>
       </c>
     </row>
     <row r="25">
@@ -896,13 +896,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="D25" t="n">
-        <v>56.15</v>
+        <v>52.9</v>
       </c>
       <c r="E25" t="n">
-        <v>168.45</v>
+        <v>1904.4</v>
       </c>
     </row>
     <row r="26">
@@ -917,13 +917,13 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>67.33</v>
+        <v>70.91</v>
       </c>
       <c r="E26" t="n">
-        <v>7136.98</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -941,7 +941,7 @@
         <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>82.42</v>
+        <v>85.62</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -959,13 +959,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>18</v>
+        <v>89</v>
       </c>
       <c r="D28" t="n">
-        <v>423.51</v>
+        <v>437.55</v>
       </c>
       <c r="E28" t="n">
-        <v>7623.18</v>
+        <v>38941.95</v>
       </c>
     </row>
     <row r="29">
@@ -980,13 +980,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="D29" t="n">
-        <v>348.42</v>
+        <v>339.69</v>
       </c>
       <c r="E29" t="n">
-        <v>31357.8</v>
+        <v>6454.11</v>
       </c>
     </row>
     <row r="30">
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="D30" t="n">
-        <v>554.25</v>
+        <v>554.47</v>
       </c>
       <c r="E30" t="n">
-        <v>12747.75</v>
+        <v>21069.86</v>
       </c>
     </row>
     <row r="31">
@@ -1022,13 +1022,13 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="D31" t="n">
-        <v>177.18</v>
+        <v>175.41</v>
       </c>
       <c r="E31" t="n">
-        <v>2834.88</v>
+        <v>6314.76</v>
       </c>
     </row>
     <row r="32">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="D32" t="n">
-        <v>153.09</v>
+        <v>166.73</v>
       </c>
       <c r="E32" t="n">
-        <v>3827.25</v>
+        <v>2000.76</v>
       </c>
     </row>
     <row r="33">
@@ -1064,13 +1064,13 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>54</v>
+        <v>25</v>
       </c>
       <c r="D33" t="n">
-        <v>130.34</v>
+        <v>126.78</v>
       </c>
       <c r="E33" t="n">
-        <v>7038.36</v>
+        <v>3169.5</v>
       </c>
     </row>
     <row r="34">
@@ -1085,13 +1085,13 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="D34" t="n">
-        <v>37.77</v>
+        <v>39.54</v>
       </c>
       <c r="E34" t="n">
-        <v>982.02</v>
+        <v>553.5599999999999</v>
       </c>
     </row>
     <row r="35">
@@ -1106,13 +1106,13 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>482</v>
+        <v>15</v>
       </c>
       <c r="D35" t="n">
-        <v>45.29</v>
+        <v>45.91</v>
       </c>
       <c r="E35" t="n">
-        <v>21829.78</v>
+        <v>688.65</v>
       </c>
     </row>
     <row r="36">
@@ -1130,7 +1130,7 @@
         <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>88.69</v>
+        <v>85.62</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
@@ -1148,13 +1148,13 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>469</v>
+        <v>85</v>
       </c>
       <c r="D37" t="n">
-        <v>45.9</v>
+        <v>45.53</v>
       </c>
       <c r="E37" t="n">
-        <v>21527.1</v>
+        <v>3870.05</v>
       </c>
     </row>
     <row r="38">
@@ -1169,13 +1169,13 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>190</v>
+        <v>14</v>
       </c>
       <c r="D38" t="n">
-        <v>50.59</v>
+        <v>52.71</v>
       </c>
       <c r="E38" t="n">
-        <v>9612.1</v>
+        <v>737.9400000000001</v>
       </c>
     </row>
     <row r="39">
@@ -1190,13 +1190,13 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="D39" t="n">
-        <v>57.79</v>
+        <v>61.41</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>2210.76</v>
       </c>
     </row>
     <row r="40">
@@ -1211,13 +1211,13 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>99</v>
+        <v>32</v>
       </c>
       <c r="D40" t="n">
-        <v>71.83</v>
+        <v>69.19</v>
       </c>
       <c r="E40" t="n">
-        <v>7111.17</v>
+        <v>2214.08</v>
       </c>
     </row>
     <row r="41">
@@ -1232,13 +1232,13 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="D41" t="n">
-        <v>99.33</v>
+        <v>99.29000000000001</v>
       </c>
       <c r="E41" t="n">
-        <v>1787.94</v>
+        <v>4368.76</v>
       </c>
     </row>
     <row r="42">
@@ -1253,13 +1253,13 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="D42" t="n">
-        <v>74.28</v>
+        <v>71.27</v>
       </c>
       <c r="E42" t="n">
-        <v>1559.88</v>
+        <v>2351.91</v>
       </c>
     </row>
     <row r="43">
@@ -1274,13 +1274,13 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>47</v>
+        <v>6</v>
       </c>
       <c r="D43" t="n">
-        <v>54.04</v>
+        <v>58.32</v>
       </c>
       <c r="E43" t="n">
-        <v>2539.88</v>
+        <v>349.92</v>
       </c>
     </row>
     <row r="44">
@@ -1295,13 +1295,13 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>81</v>
+        <v>19</v>
       </c>
       <c r="D44" t="n">
-        <v>472.91</v>
+        <v>461.92</v>
       </c>
       <c r="E44" t="n">
-        <v>38305.71</v>
+        <v>8776.48</v>
       </c>
     </row>
     <row r="45">
@@ -1316,13 +1316,13 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>178.76</v>
+        <v>172.08</v>
       </c>
       <c r="E45" t="n">
-        <v>3038.92</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -1337,13 +1337,13 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>29</v>
+        <v>67</v>
       </c>
       <c r="D46" t="n">
-        <v>35.25</v>
+        <v>36.38</v>
       </c>
       <c r="E46" t="n">
-        <v>1022.25</v>
+        <v>2437.46</v>
       </c>
     </row>
     <row r="47">
@@ -1358,13 +1358,13 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>91</v>
+        <v>36</v>
       </c>
       <c r="D47" t="n">
-        <v>31.04</v>
+        <v>32.8</v>
       </c>
       <c r="E47" t="n">
-        <v>2824.64</v>
+        <v>1180.8</v>
       </c>
     </row>
     <row r="48">
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>9</v>
+        <v>69</v>
       </c>
       <c r="D48" t="n">
-        <v>44.13</v>
+        <v>41.29</v>
       </c>
       <c r="E48" t="n">
-        <v>397.17</v>
+        <v>2849.01</v>
       </c>
     </row>
     <row r="49">
@@ -1400,13 +1400,13 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="D49" t="n">
-        <v>49.91</v>
+        <v>51.21</v>
       </c>
       <c r="E49" t="n">
-        <v>1098.02</v>
+        <v>1536.3</v>
       </c>
     </row>
     <row r="50">
@@ -1421,13 +1421,13 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="D50" t="n">
-        <v>274.16</v>
+        <v>269.82</v>
       </c>
       <c r="E50" t="n">
-        <v>1096.64</v>
+        <v>3777.48</v>
       </c>
     </row>
     <row r="51">
@@ -1442,13 +1442,13 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="D51" t="n">
-        <v>61.96</v>
+        <v>61.76</v>
       </c>
       <c r="E51" t="n">
-        <v>495.68</v>
+        <v>2161.6</v>
       </c>
     </row>
     <row r="52">
@@ -1463,13 +1463,13 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="D52" t="n">
-        <v>116.32</v>
+        <v>112.99</v>
       </c>
       <c r="E52" t="n">
-        <v>0</v>
+        <v>5084.55</v>
       </c>
     </row>
     <row r="53">
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="D53" t="n">
-        <v>55.53</v>
+        <v>54.19</v>
       </c>
       <c r="E53" t="n">
-        <v>277.65</v>
+        <v>1354.75</v>
       </c>
     </row>
     <row r="54">
@@ -1505,13 +1505,13 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="D54" t="n">
-        <v>159.1</v>
+        <v>167.03</v>
       </c>
       <c r="E54" t="n">
-        <v>3977.5</v>
+        <v>3006.54</v>
       </c>
     </row>
     <row r="55">
@@ -1526,13 +1526,13 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>436</v>
+        <v>10</v>
       </c>
       <c r="D55" t="n">
-        <v>198.11</v>
+        <v>198.21</v>
       </c>
       <c r="E55" t="n">
-        <v>86375.96000000001</v>
+        <v>1982.1</v>
       </c>
     </row>
     <row r="56">
@@ -1547,13 +1547,13 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="D56" t="n">
-        <v>86.45</v>
+        <v>85.17</v>
       </c>
       <c r="E56" t="n">
-        <v>2420.6</v>
+        <v>1362.72</v>
       </c>
     </row>
     <row r="57">
@@ -1568,13 +1568,13 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="D57" t="n">
-        <v>72.98</v>
+        <v>73.54000000000001</v>
       </c>
       <c r="E57" t="n">
-        <v>875.76</v>
+        <v>2647.44</v>
       </c>
     </row>
     <row r="58">
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D58" t="n">
-        <v>27.34</v>
+        <v>28</v>
       </c>
       <c r="E58" t="n">
-        <v>246.06</v>
+        <v>140</v>
       </c>
     </row>
     <row r="59">
@@ -1610,13 +1610,13 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="D59" t="n">
-        <v>38.97</v>
+        <v>39.26</v>
       </c>
       <c r="E59" t="n">
-        <v>506.61</v>
+        <v>1295.58</v>
       </c>
     </row>
     <row r="60">
@@ -1631,13 +1631,13 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>30</v>
+        <v>79</v>
       </c>
       <c r="D60" t="n">
-        <v>793.14</v>
+        <v>792.15</v>
       </c>
       <c r="E60" t="n">
-        <v>23794.2</v>
+        <v>62579.85</v>
       </c>
     </row>
     <row r="61">
@@ -1652,13 +1652,13 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>14</v>
+        <v>76</v>
       </c>
       <c r="D61" t="n">
-        <v>1129.99</v>
+        <v>1138.34</v>
       </c>
       <c r="E61" t="n">
-        <v>15819.86</v>
+        <v>86513.84</v>
       </c>
     </row>
     <row r="62">
@@ -1673,13 +1673,13 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>83</v>
+        <v>29</v>
       </c>
       <c r="D62" t="n">
-        <v>636.99</v>
+        <v>612.75</v>
       </c>
       <c r="E62" t="n">
-        <v>52870.17</v>
+        <v>17769.75</v>
       </c>
     </row>
     <row r="63">
@@ -1694,13 +1694,13 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>3</v>
+        <v>81</v>
       </c>
       <c r="D63" t="n">
-        <v>819.85</v>
+        <v>860.64</v>
       </c>
       <c r="E63" t="n">
-        <v>2459.55</v>
+        <v>69711.84</v>
       </c>
     </row>
     <row r="64">
@@ -1715,13 +1715,13 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="D64" t="n">
-        <v>118.84</v>
+        <v>109.13</v>
       </c>
       <c r="E64" t="n">
-        <v>3565.2</v>
+        <v>2400.86</v>
       </c>
     </row>
     <row r="65">
@@ -1736,13 +1736,13 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D65" t="n">
-        <v>142.34</v>
+        <v>137.5</v>
       </c>
       <c r="E65" t="n">
-        <v>4127.86</v>
+        <v>3712.5</v>
       </c>
     </row>
     <row r="66">
@@ -1757,13 +1757,13 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>56</v>
+        <v>152</v>
       </c>
       <c r="D66" t="n">
-        <v>424.67</v>
+        <v>397.89</v>
       </c>
       <c r="E66" t="n">
-        <v>23781.52</v>
+        <v>60479.28</v>
       </c>
     </row>
     <row r="67">
@@ -1778,13 +1778,13 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="D67" t="n">
-        <v>212.26</v>
+        <v>224.04</v>
       </c>
       <c r="E67" t="n">
-        <v>1910.34</v>
+        <v>5825.04</v>
       </c>
     </row>
     <row r="68">
@@ -1799,13 +1799,13 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="D68" t="n">
-        <v>267.14</v>
+        <v>283</v>
       </c>
       <c r="E68" t="n">
-        <v>11754.16</v>
+        <v>6509</v>
       </c>
     </row>
     <row r="69">
@@ -1820,13 +1820,13 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D69" t="n">
-        <v>174.9</v>
+        <v>171.72</v>
       </c>
       <c r="E69" t="n">
-        <v>5771.7</v>
+        <v>6181.92</v>
       </c>
     </row>
     <row r="70">
@@ -1841,13 +1841,13 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="D70" t="n">
-        <v>61.32</v>
+        <v>66.03</v>
       </c>
       <c r="E70" t="n">
-        <v>0</v>
+        <v>1782.81</v>
       </c>
     </row>
     <row r="71">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>49</v>
+        <v>493</v>
       </c>
       <c r="D71" t="n">
-        <v>30.3</v>
+        <v>28.1</v>
       </c>
       <c r="E71" t="n">
-        <v>1484.7</v>
+        <v>13853.3</v>
       </c>
     </row>
     <row r="72">
@@ -1883,13 +1883,13 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="D72" t="n">
-        <v>32.36</v>
+        <v>35.2</v>
       </c>
       <c r="E72" t="n">
-        <v>194.16</v>
+        <v>950.4</v>
       </c>
     </row>
     <row r="73">
@@ -1904,13 +1904,13 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="D73" t="n">
-        <v>27.24</v>
+        <v>27.72</v>
       </c>
       <c r="E73" t="n">
-        <v>435.84</v>
+        <v>1219.68</v>
       </c>
     </row>
     <row r="74">
@@ -1925,13 +1925,13 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D74" t="n">
-        <v>37.27</v>
+        <v>34.91</v>
       </c>
       <c r="E74" t="n">
-        <v>223.62</v>
+        <v>418.92</v>
       </c>
     </row>
     <row r="75">
@@ -1946,13 +1946,13 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>102</v>
+        <v>25</v>
       </c>
       <c r="D75" t="n">
-        <v>207.98</v>
+        <v>204.01</v>
       </c>
       <c r="E75" t="n">
-        <v>21213.96</v>
+        <v>5100.25</v>
       </c>
     </row>
     <row r="76">
@@ -1967,13 +1967,13 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D76" t="n">
-        <v>395.29</v>
+        <v>432.8</v>
       </c>
       <c r="E76" t="n">
-        <v>14230.44</v>
+        <v>13849.6</v>
       </c>
     </row>
     <row r="77">
@@ -1988,13 +1988,13 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="D77" t="n">
-        <v>253.77</v>
+        <v>275.27</v>
       </c>
       <c r="E77" t="n">
-        <v>19032.75</v>
+        <v>18718.36</v>
       </c>
     </row>
     <row r="78">
@@ -2009,13 +2009,13 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D78" t="n">
-        <v>358.34</v>
+        <v>360.02</v>
       </c>
       <c r="E78" t="n">
-        <v>11108.54</v>
+        <v>10800.6</v>
       </c>
     </row>
     <row r="79">
@@ -2030,13 +2030,13 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="D79" t="n">
-        <v>76.88</v>
+        <v>79.68000000000001</v>
       </c>
       <c r="E79" t="n">
-        <v>3382.72</v>
+        <v>557.76</v>
       </c>
     </row>
     <row r="80">
@@ -2051,13 +2051,13 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>89</v>
+        <v>15</v>
       </c>
       <c r="D80" t="n">
-        <v>115.05</v>
+        <v>118.75</v>
       </c>
       <c r="E80" t="n">
-        <v>10239.45</v>
+        <v>1781.25</v>
       </c>
     </row>
     <row r="81">
@@ -2072,13 +2072,13 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>203</v>
+        <v>0</v>
       </c>
       <c r="D81" t="n">
-        <v>429.68</v>
+        <v>433.1</v>
       </c>
       <c r="E81" t="n">
-        <v>87225.03999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -2093,13 +2093,13 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D82" t="n">
-        <v>1823.97</v>
+        <v>1846.06</v>
       </c>
       <c r="E82" t="n">
-        <v>63838.95</v>
+        <v>62766.04</v>
       </c>
     </row>
     <row r="83">
@@ -2117,7 +2117,7 @@
         <v>0</v>
       </c>
       <c r="D83" t="n">
-        <v>113.78</v>
+        <v>112.97</v>
       </c>
       <c r="E83" t="n">
         <v>0</v>
@@ -2135,13 +2135,13 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="D84" t="n">
-        <v>82.95999999999999</v>
+        <v>78.48</v>
       </c>
       <c r="E84" t="n">
-        <v>2571.76</v>
+        <v>1412.64</v>
       </c>
     </row>
   </sheetData>
